--- a/api/clv3/xlsx/pt/FinanceType.xlsx
+++ b/api/clv3/xlsx/pt/FinanceType.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="165">
   <si>
     <t>code</t>
   </si>
@@ -200,6 +200,9 @@
   </si>
   <si>
     <t>Outros instrumentos híbridos</t>
+  </si>
+  <si>
+    <t>434</t>
   </si>
   <si>
     <t>451</t>
@@ -837,7 +840,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1216,25 +1219,22 @@
       <c r="A28" t="s">
         <v>62</v>
       </c>
-      <c r="B28" t="s">
-        <v>63</v>
-      </c>
       <c r="C28" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D28" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
+        <v>63</v>
+      </c>
+      <c r="B29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" t="s">
         <v>65</v>
-      </c>
-      <c r="B29" t="s">
-        <v>66</v>
-      </c>
-      <c r="C29" t="s">
-        <v>33</v>
       </c>
       <c r="D29" t="s">
         <v>16</v>
@@ -1242,10 +1242,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" t="s">
         <v>67</v>
-      </c>
-      <c r="B30" t="s">
-        <v>68</v>
       </c>
       <c r="C30" t="s">
         <v>33</v>
@@ -1256,41 +1256,41 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" t="s">
         <v>69</v>
       </c>
-      <c r="B31" t="s">
-        <v>70</v>
-      </c>
       <c r="C31" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="D31" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" t="s">
         <v>72</v>
       </c>
-      <c r="B32" t="s">
-        <v>73</v>
-      </c>
-      <c r="C32" t="s">
-        <v>71</v>
-      </c>
       <c r="D32" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" t="s">
         <v>74</v>
       </c>
-      <c r="B33" t="s">
-        <v>75</v>
-      </c>
       <c r="C33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D33" t="s">
         <v>16</v>
@@ -1298,27 +1298,27 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
+        <v>75</v>
+      </c>
+      <c r="B34" t="s">
         <v>76</v>
       </c>
-      <c r="B34" t="s">
-        <v>77</v>
-      </c>
       <c r="C34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D34" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
+        <v>77</v>
+      </c>
+      <c r="B35" t="s">
         <v>78</v>
       </c>
-      <c r="B35" t="s">
-        <v>79</v>
-      </c>
       <c r="C35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
@@ -1326,13 +1326,13 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
+        <v>79</v>
+      </c>
+      <c r="B36" t="s">
         <v>80</v>
       </c>
-      <c r="B36" t="s">
-        <v>81</v>
-      </c>
       <c r="C36" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D36" t="s">
         <v>7</v>
@@ -1340,13 +1340,13 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B37" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C37" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
@@ -1354,13 +1354,13 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
+        <v>84</v>
+      </c>
+      <c r="B38" t="s">
         <v>85</v>
       </c>
-      <c r="B38" t="s">
-        <v>86</v>
-      </c>
       <c r="C38" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D38" t="s">
         <v>7</v>
@@ -1368,13 +1368,13 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" t="s">
         <v>87</v>
       </c>
-      <c r="B39" t="s">
-        <v>88</v>
-      </c>
       <c r="C39" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
@@ -1382,13 +1382,13 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
+        <v>88</v>
+      </c>
+      <c r="B40" t="s">
         <v>89</v>
       </c>
-      <c r="B40" t="s">
-        <v>90</v>
-      </c>
       <c r="C40" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D40" t="s">
         <v>7</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" t="s">
         <v>91</v>
       </c>
-      <c r="B41" t="s">
-        <v>92</v>
-      </c>
       <c r="C41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D41" t="s">
         <v>7</v>
@@ -1410,13 +1410,13 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
+        <v>92</v>
+      </c>
+      <c r="B42" t="s">
         <v>93</v>
       </c>
-      <c r="B42" t="s">
-        <v>94</v>
-      </c>
       <c r="C42" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D42" t="s">
         <v>7</v>
@@ -1424,13 +1424,13 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
+        <v>94</v>
+      </c>
+      <c r="B43" t="s">
         <v>95</v>
       </c>
-      <c r="B43" t="s">
-        <v>96</v>
-      </c>
       <c r="C43" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
@@ -1438,13 +1438,13 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
+        <v>96</v>
+      </c>
+      <c r="B44" t="s">
         <v>97</v>
       </c>
-      <c r="B44" t="s">
-        <v>98</v>
-      </c>
       <c r="C44" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
@@ -1452,13 +1452,13 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
+        <v>98</v>
+      </c>
+      <c r="B45" t="s">
         <v>99</v>
       </c>
-      <c r="B45" t="s">
-        <v>100</v>
-      </c>
       <c r="C45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
@@ -1466,13 +1466,13 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
+        <v>100</v>
+      </c>
+      <c r="B46" t="s">
         <v>101</v>
       </c>
-      <c r="B46" t="s">
-        <v>102</v>
-      </c>
       <c r="C46" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -1480,13 +1480,13 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
+        <v>102</v>
+      </c>
+      <c r="B47" t="s">
         <v>103</v>
       </c>
-      <c r="B47" t="s">
-        <v>104</v>
-      </c>
       <c r="C47" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
@@ -1494,13 +1494,13 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
+        <v>104</v>
+      </c>
+      <c r="B48" t="s">
         <v>105</v>
       </c>
-      <c r="B48" t="s">
-        <v>106</v>
-      </c>
       <c r="C48" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -1508,13 +1508,13 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
+        <v>106</v>
+      </c>
+      <c r="B49" t="s">
         <v>107</v>
       </c>
-      <c r="B49" t="s">
-        <v>108</v>
-      </c>
       <c r="C49" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -1522,13 +1522,13 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
+        <v>108</v>
+      </c>
+      <c r="B50" t="s">
         <v>109</v>
       </c>
-      <c r="B50" t="s">
-        <v>110</v>
-      </c>
       <c r="C50" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
@@ -1536,13 +1536,13 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
+        <v>110</v>
+      </c>
+      <c r="B51" t="s">
         <v>111</v>
       </c>
-      <c r="B51" t="s">
-        <v>112</v>
-      </c>
       <c r="C51" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
@@ -1550,13 +1550,13 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
+        <v>112</v>
+      </c>
+      <c r="B52" t="s">
         <v>113</v>
       </c>
-      <c r="B52" t="s">
-        <v>114</v>
-      </c>
       <c r="C52" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
@@ -1564,13 +1564,13 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
+        <v>114</v>
+      </c>
+      <c r="B53" t="s">
         <v>115</v>
       </c>
-      <c r="B53" t="s">
-        <v>116</v>
-      </c>
       <c r="C53" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
@@ -1578,13 +1578,13 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
+        <v>116</v>
+      </c>
+      <c r="B54" t="s">
         <v>117</v>
       </c>
-      <c r="B54" t="s">
-        <v>118</v>
-      </c>
       <c r="C54" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
@@ -1592,13 +1592,13 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
+        <v>118</v>
+      </c>
+      <c r="B55" t="s">
         <v>119</v>
       </c>
-      <c r="B55" t="s">
-        <v>120</v>
-      </c>
       <c r="C55" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
@@ -1606,13 +1606,13 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
+        <v>120</v>
+      </c>
+      <c r="B56" t="s">
         <v>121</v>
       </c>
-      <c r="B56" t="s">
-        <v>122</v>
-      </c>
       <c r="C56" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
@@ -1620,13 +1620,13 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
+        <v>122</v>
+      </c>
+      <c r="B57" t="s">
         <v>123</v>
       </c>
-      <c r="B57" t="s">
-        <v>124</v>
-      </c>
       <c r="C57" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
+        <v>124</v>
+      </c>
+      <c r="B58" t="s">
         <v>125</v>
       </c>
-      <c r="B58" t="s">
-        <v>126</v>
-      </c>
       <c r="C58" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
@@ -1648,13 +1648,13 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
+        <v>126</v>
+      </c>
+      <c r="B59" t="s">
         <v>127</v>
       </c>
-      <c r="B59" t="s">
-        <v>128</v>
-      </c>
       <c r="C59" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
@@ -1662,13 +1662,13 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
+        <v>128</v>
+      </c>
+      <c r="B60" t="s">
         <v>129</v>
       </c>
-      <c r="B60" t="s">
-        <v>130</v>
-      </c>
       <c r="C60" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
@@ -1676,13 +1676,13 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
+        <v>130</v>
+      </c>
+      <c r="B61" t="s">
         <v>131</v>
       </c>
-      <c r="B61" t="s">
-        <v>132</v>
-      </c>
       <c r="C61" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D61" t="s">
         <v>7</v>
@@ -1690,13 +1690,13 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
+        <v>132</v>
+      </c>
+      <c r="B62" t="s">
         <v>133</v>
       </c>
-      <c r="B62" t="s">
-        <v>134</v>
-      </c>
       <c r="C62" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
@@ -1704,10 +1704,13 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
+        <v>134</v>
+      </c>
+      <c r="B63" t="s">
         <v>135</v>
       </c>
       <c r="C63" t="s">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="D63" t="s">
         <v>7</v>
@@ -1794,25 +1797,22 @@
       <c r="A71" t="s">
         <v>143</v>
       </c>
-      <c r="B71" t="s">
-        <v>144</v>
-      </c>
       <c r="C71" t="s">
-        <v>145</v>
+        <v>13</v>
       </c>
       <c r="D71" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
+        <v>144</v>
+      </c>
+      <c r="B72" t="s">
+        <v>145</v>
+      </c>
+      <c r="C72" t="s">
         <v>146</v>
-      </c>
-      <c r="B72" t="s">
-        <v>147</v>
-      </c>
-      <c r="C72" t="s">
-        <v>145</v>
       </c>
       <c r="D72" t="s">
         <v>16</v>
@@ -1820,13 +1820,13 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
+        <v>147</v>
+      </c>
+      <c r="B73" t="s">
         <v>148</v>
       </c>
-      <c r="B73" t="s">
-        <v>149</v>
-      </c>
       <c r="C73" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D73" t="s">
         <v>16</v>
@@ -1834,13 +1834,13 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
+        <v>149</v>
+      </c>
+      <c r="B74" t="s">
         <v>150</v>
       </c>
-      <c r="B74" t="s">
-        <v>151</v>
-      </c>
       <c r="C74" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D74" t="s">
         <v>16</v>
@@ -1848,13 +1848,13 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
+        <v>151</v>
+      </c>
+      <c r="B75" t="s">
+        <v>152</v>
+      </c>
+      <c r="C75" t="s">
         <v>153</v>
-      </c>
-      <c r="B75" t="s">
-        <v>154</v>
-      </c>
-      <c r="C75" t="s">
-        <v>152</v>
       </c>
       <c r="D75" t="s">
         <v>16</v>
@@ -1862,13 +1862,13 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
+        <v>154</v>
+      </c>
+      <c r="B76" t="s">
         <v>155</v>
       </c>
-      <c r="B76" t="s">
-        <v>156</v>
-      </c>
       <c r="C76" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D76" t="s">
         <v>16</v>
@@ -1876,13 +1876,13 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
+        <v>156</v>
+      </c>
+      <c r="B77" t="s">
+        <v>157</v>
+      </c>
+      <c r="C77" t="s">
         <v>158</v>
-      </c>
-      <c r="B77" t="s">
-        <v>159</v>
-      </c>
-      <c r="C77" t="s">
-        <v>157</v>
       </c>
       <c r="D77" t="s">
         <v>16</v>
@@ -1890,13 +1890,13 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
+        <v>159</v>
+      </c>
+      <c r="B78" t="s">
         <v>160</v>
       </c>
-      <c r="B78" t="s">
-        <v>161</v>
-      </c>
       <c r="C78" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D78" t="s">
         <v>16</v>
@@ -1904,15 +1904,29 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
+        <v>161</v>
+      </c>
+      <c r="B79" t="s">
         <v>162</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C79" t="s">
+        <v>158</v>
+      </c>
+      <c r="D79" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" t="s">
         <v>163</v>
       </c>
-      <c r="C79" t="s">
-        <v>157</v>
-      </c>
-      <c r="D79" t="s">
+      <c r="B80" t="s">
+        <v>164</v>
+      </c>
+      <c r="C80" t="s">
+        <v>158</v>
+      </c>
+      <c r="D80" t="s">
         <v>16</v>
       </c>
     </row>
